--- a/data/trans_orig/IQ28_T-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_T-Edad-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Talla media, en centímetros, recogida tras medición</t>
+          <t>Talla media, en centímetros, recogida tras medición (tasa de respuesta: 93,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,09; 88,93</t>
+          <t>83,07; 88,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82,82; 88,02</t>
+          <t>82,66; 88,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99,67; 121,51</t>
+          <t>98,33; 120,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85,0; 91,51</t>
+          <t>85,21; 91,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,76; 93,07</t>
+          <t>87,02; 93,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,52; 110,39</t>
+          <t>90,64; 110,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,8; 89,32</t>
+          <t>84,99; 89,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>85,41; 89,91</t>
+          <t>85,48; 89,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>97,74; 113,95</t>
+          <t>97,79; 113,22</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>109,43; 112,11</t>
+          <t>109,23; 112,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>110,88; 113,9</t>
+          <t>110,97; 113,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107,75; 118,51</t>
+          <t>108,15; 118,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>108,9; 111,43</t>
+          <t>108,93; 111,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>110,38; 113,41</t>
+          <t>110,7; 113,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>115,94; 123,73</t>
+          <t>116,38; 123,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>109,61; 111,38</t>
+          <t>109,48; 111,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>111,28; 113,12</t>
+          <t>111,18; 113,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>114,15; 120,34</t>
+          <t>114,04; 120,23</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>135,58; 138,93</t>
+          <t>135,4; 138,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>137,63; 140,18</t>
+          <t>137,64; 140,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132,67; 142,5</t>
+          <t>132,6; 142,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>135,04; 137,99</t>
+          <t>134,89; 138,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>137,95; 140,39</t>
+          <t>137,68; 140,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>138,63; 144,97</t>
+          <t>138,73; 144,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>135,68; 138,07</t>
+          <t>135,57; 137,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>138,18; 139,85</t>
+          <t>138,12; 139,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>136,95; 142,68</t>
+          <t>137,2; 142,77</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>155,6; 158,21</t>
+          <t>155,54; 158,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>156,28; 158,95</t>
+          <t>156,35; 158,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151,21; 158,05</t>
+          <t>150,84; 158,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160,58; 163,76</t>
+          <t>160,58; 163,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>160,88; 163,8</t>
+          <t>160,88; 163,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>151,1; 158,66</t>
+          <t>150,97; 158,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>158,54; 160,71</t>
+          <t>158,42; 160,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>159,02; 161,02</t>
+          <t>159,13; 161,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>152,26; 157,37</t>
+          <t>152,33; 157,25</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>127,5; 130,83</t>
+          <t>127,54; 130,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>130,51; 133,66</t>
+          <t>130,44; 133,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>134,98; 145,4</t>
+          <t>135,0; 144,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128,32; 131,92</t>
+          <t>128,44; 131,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>130,54; 133,79</t>
+          <t>130,52; 133,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>137,77; 142,73</t>
+          <t>137,86; 143,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>128,44; 130,85</t>
+          <t>128,6; 130,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>130,92; 133,24</t>
+          <t>130,94; 133,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>137,38; 142,78</t>
+          <t>137,28; 142,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_T-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_T-Edad-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Talla media, en centímetros, recogida tras medición (tasa de respuesta: 93,78%)</t>
+          <t>Talla media, en centímetros, recogida por medición (tasa de respuesta: 93,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,07; 88,79</t>
+          <t>83,13; 88,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82,66; 88,37</t>
+          <t>82,58; 88,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98,33; 120,77</t>
+          <t>98,59; 121,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85,21; 91,65</t>
+          <t>85,08; 91,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,02; 93,16</t>
+          <t>87,05; 93,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,64; 110,38</t>
+          <t>90,55; 110,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,99; 89,34</t>
+          <t>84,86; 89,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>85,48; 89,64</t>
+          <t>85,62; 89,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>97,79; 113,22</t>
+          <t>98,03; 112,25</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>109,23; 112,12</t>
+          <t>109,36; 112,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>110,97; 113,84</t>
+          <t>110,78; 113,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>108,15; 118,47</t>
+          <t>108,79; 118,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>108,93; 111,46</t>
+          <t>109,01; 111,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>110,7; 113,61</t>
+          <t>110,57; 113,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>116,38; 123,84</t>
+          <t>116,07; 123,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -822,12 +822,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>111,18; 113,18</t>
+          <t>111,31; 113,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>114,04; 120,23</t>
+          <t>114,1; 120,27</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>135,4; 138,72</t>
+          <t>135,32; 138,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>137,64; 140,27</t>
+          <t>137,77; 140,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132,6; 142,69</t>
+          <t>132,53; 142,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>134,89; 138,08</t>
+          <t>135,05; 138,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>137,68; 140,24</t>
+          <t>137,77; 140,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>138,73; 144,78</t>
+          <t>138,89; 145,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>135,57; 137,92</t>
+          <t>135,65; 137,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>138,12; 139,94</t>
+          <t>138,19; 139,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>137,2; 142,77</t>
+          <t>137,07; 142,72</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>155,54; 158,12</t>
+          <t>155,51; 158,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>156,35; 158,95</t>
+          <t>156,32; 158,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150,84; 158,01</t>
+          <t>150,99; 157,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160,58; 163,84</t>
+          <t>160,65; 163,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>160,88; 163,86</t>
+          <t>160,89; 163,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>150,97; 158,24</t>
+          <t>150,97; 158,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>158,42; 160,62</t>
+          <t>158,57; 160,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>159,13; 161,17</t>
+          <t>159,05; 161,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>152,33; 157,25</t>
+          <t>152,1; 157,19</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>127,54; 130,88</t>
+          <t>127,44; 130,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>130,44; 133,69</t>
+          <t>130,37; 133,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>135,0; 144,97</t>
+          <t>135,33; 146,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128,44; 131,98</t>
+          <t>128,56; 131,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>130,52; 133,84</t>
+          <t>130,42; 133,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>137,86; 143,05</t>
+          <t>137,61; 142,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>128,6; 130,91</t>
+          <t>128,65; 130,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>130,94; 133,26</t>
+          <t>130,96; 133,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>137,28; 142,7</t>
+          <t>137,22; 142,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_T-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_T-Edad-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>88,7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>89,21</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>98,89</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>86,08</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>85,93</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>108,85</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>88,7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>89,21</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>99,26</t>
+          <t>108,98</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>104,83</t>
+          <t>105,16</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,13; 88,8</t>
+          <t>85,0; 91,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82,58; 88,48</t>
+          <t>86,76; 93,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98,59; 121,33</t>
+          <t>90,4; 110,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85,08; 91,97</t>
+          <t>83,09; 88,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,05; 93,34</t>
+          <t>82,82; 88,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,55; 110,77</t>
+          <t>99,29; 121,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,86; 89,34</t>
+          <t>84,8; 89,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>85,62; 89,82</t>
+          <t>85,41; 89,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>98,03; 112,25</t>
+          <t>98,18; 114,49</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>110,21</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112,05</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>119,82</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>110,81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>112,42</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114,57</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>110,21</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>112,05</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>119,6</t>
+          <t>116,39</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>117,51</t>
+          <t>118,35</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>109,36; 112,19</t>
+          <t>108,9; 111,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>110,78; 113,78</t>
+          <t>110,38; 113,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>108,79; 118,63</t>
+          <t>116,22; 124,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>109,01; 111,37</t>
+          <t>109,43; 112,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>110,57; 113,4</t>
+          <t>110,88; 113,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>116,07; 123,62</t>
+          <t>112,57; 120,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>109,48; 111,37</t>
+          <t>109,61; 111,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>111,31; 113,4</t>
+          <t>111,28; 113,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>114,1; 120,27</t>
+          <t>115,95; 121,09</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>136,6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>139,08</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>142,35</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>137,18</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>138,94</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>137,08</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>136,6</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>139,08</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>141,9</t>
+          <t>136,54</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>139,84</t>
+          <t>139,83</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>135,32; 138,76</t>
+          <t>135,04; 137,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>137,77; 140,15</t>
+          <t>137,95; 140,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132,53; 142,46</t>
+          <t>139,07; 145,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>135,05; 138,0</t>
+          <t>135,58; 138,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>137,77; 140,27</t>
+          <t>137,63; 140,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>138,89; 145,09</t>
+          <t>132,79; 140,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>135,65; 137,92</t>
+          <t>135,68; 138,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>138,19; 139,97</t>
+          <t>138,18; 139,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>137,07; 142,72</t>
+          <t>137,07; 142,33</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>162,24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>162,45</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>155,8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>156,89</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>157,61</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>154,31</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>162,24</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>162,45</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>155,13</t>
+          <t>152,89</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>154,73</t>
+          <t>154,49</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>155,51; 158,09</t>
+          <t>160,58; 163,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>156,32; 158,82</t>
+          <t>160,88; 163,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150,99; 157,9</t>
+          <t>152,18; 158,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160,65; 163,8</t>
+          <t>155,6; 158,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>160,89; 163,93</t>
+          <t>156,28; 158,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>150,97; 158,13</t>
+          <t>149,98; 155,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>158,57; 160,72</t>
+          <t>158,54; 160,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>159,05; 161,15</t>
+          <t>159,02; 161,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>152,1; 157,19</t>
+          <t>152,29; 156,65</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>130,24</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132,13</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141,6</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>129,2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>132,08</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>138,73</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>130,24</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>132,13</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>140,26</t>
+          <t>137,72</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>139,56</t>
+          <t>139,87</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>127,44; 130,91</t>
+          <t>128,32; 131,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>130,37; 133,71</t>
+          <t>130,54; 133,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>135,33; 146,78</t>
+          <t>139,17; 143,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128,56; 131,98</t>
+          <t>127,5; 130,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>130,42; 133,75</t>
+          <t>130,51; 133,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>137,61; 142,73</t>
+          <t>135,0; 140,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>128,65; 130,94</t>
+          <t>128,44; 130,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>130,96; 133,38</t>
+          <t>130,92; 133,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>137,22; 142,97</t>
+          <t>138,08; 141,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_T-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_T-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>88,7</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>89,21</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>98,89</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>86,08</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>85,93</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>108,98</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>87,28</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>87,54</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>105,16</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>88.70436792744135</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>89.21329028184385</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>98.89015694293967</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>86.07953076591414</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>85.92561325836353</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>108.9769458495567</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>87.27771984930631</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>87.54119558476282</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>105.1622909269473</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>85,0; 91,51</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>86,76; 93,07</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>90,4; 110,46</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>83,09; 88,93</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>82,82; 88,02</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,29; 121,05</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,8; 89,32</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85,41; 89,91</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>98,18; 114,49</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>84.99888149723471</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>86.76469007532222</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>90.40471256663739</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>83.09005824114708</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>82.82032007592008</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>99.29350578161633</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>84.79969904532962</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>85.40734442122339</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>98.18127617402234</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>91.513231515866</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>93.06926216289908</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>110.4623291521219</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>88.92591844314147</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>88.024548666683</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>121.0513216808704</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>89.31829545268509</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>89.90512072587745</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>114.4897819828947</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>110,21</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>112,05</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>119,82</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>110,81</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>112,42</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>116,39</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>110,49</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>112,21</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>118,35</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>108,9; 111,43</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>110,38; 113,41</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>116,22; 124,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>109,43; 112,11</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>110,88; 113,9</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>112,57; 120,37</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>109,61; 111,38</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>111,28; 113,12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>115,95; 121,09</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>110.2085330172878</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>112.0531466889278</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>119.8163822124973</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>110.8055098193584</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>112.4157651920813</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>116.3898079191093</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>110.4876892775593</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>112.213812800883</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>118.3526516578144</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>136,6</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>139,08</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>142,35</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>137,18</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>138,94</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>136,54</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>136,89</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139,01</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>139,83</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>108.904119266493</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>110.37799439635</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>116.2174350320589</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>109.4303063971371</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>110.8800609036998</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>112.5712202837144</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>109.6094830918608</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>111.2848808232764</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>115.9463168866317</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>135,04; 137,99</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>137,95; 140,39</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>139,07; 145,44</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>135,58; 138,93</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>137,63; 140,18</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>132,79; 140,54</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>135,68; 138,07</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>138,18; 139,85</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>137,07; 142,33</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>111.4278884322822</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>113.4120514232149</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>124.0033471590745</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>112.1083155774502</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>113.895562581436</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>120.3674466914923</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>111.3802516392511</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>113.1185017630489</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>121.090438422385</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,217 +845,324 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>162,24</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>162,45</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>155,8</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>156,89</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>157,61</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>152,89</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>159,61</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>160,07</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>154,49</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>136.5998426751799</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>139.0812078976731</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>142.3459423817628</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>137.1832705293436</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>138.9395509278141</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>136.5403541988284</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>136.8901080944971</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>139.0097824712695</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>139.8326712846384</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>160,58; 163,76</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>160,88; 163,8</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>152,18; 158,74</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>155,6; 158,21</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>156,28; 158,95</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>149,98; 155,24</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>158,54; 160,71</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>159,02; 161,02</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>152,29; 156,65</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>135.0419299499546</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>137.9464026282623</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>139.0729514814439</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>135.5796664663081</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>137.6295930806759</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>132.7901314474017</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>135.67789415748</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>138.1754598183075</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>137.0724118462147</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>137.985642948923</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>140.3923070101486</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>145.4354807494766</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>138.927519492386</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>140.1827373677557</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>140.537246096034</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>138.0713744068752</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>139.854297932554</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>142.3285442453681</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>162.2399119051433</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>162.4450805671693</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>155.804628684396</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>156.8903153887572</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>157.6135384245117</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>152.8882719202711</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>159.6069507458922</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>160.0748896690131</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>154.489657351337</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>160.5763337243295</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>160.8829557927588</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>152.1776934573864</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>155.5983598690959</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>156.2795572788358</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>149.9838234816758</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>158.5354795492864</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>159.0248796842278</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>152.2866648175697</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>163.7578399255826</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>163.7998024561323</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>158.7382874039912</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>158.2078695023436</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>158.9458279380497</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>155.2392371577312</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>160.7130726129536</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>161.0207081461844</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>156.6548614996868</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>130,24</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>132,13</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>141,6</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>129,2</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>132,08</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>137,72</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>129,73</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>132,11</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139,87</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>128,32; 131,92</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>130,54; 133,79</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>139,17; 143,97</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>127,5; 130,83</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>130,51; 133,66</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>135,0; 140,09</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>128,44; 130,85</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>130,92; 133,24</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>138,08; 141,53</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>130.2362463963616</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>132.126185039651</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>141.5953066873152</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>129.2002785025321</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>132.082728575989</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>137.7182405143118</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>129.7318211495245</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>132.1054200025506</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>139.8652017151321</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>128.3204913877227</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>130.5365812752016</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>139.1681920408439</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>127.503702981282</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>130.5102806614116</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>134.9993367631664</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>128.4353032755952</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>130.9228089995232</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>138.0774638792128</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>131.9205990730071</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>133.7879126949009</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>143.9689690384212</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>130.8320922549772</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>133.6635327835879</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>140.0874486762942</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>130.8501360931354</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>133.2420242039933</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>141.5273966735468</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1171,14 +1171,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
